--- a/Data/Test_case/添加品牌.xlsx
+++ b/Data/Test_case/添加品牌.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mall购物商城测试项目\-01\Data\Test_case\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15963E95-9D15-47C9-92BF-CF0CDE68D4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="添加品牌" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>序号</t>
   </si>
@@ -49,68 +43,51 @@
     <t>正常添加-必填字段</t>
   </si>
   <si>
+    <t>正常添加-全部字段</t>
+  </si>
+  <si>
     <t>P0</t>
   </si>
   <si>
     <t>/brand/create</t>
   </si>
   <si>
-    <t>code=200;message=操作成功</t>
-  </si>
-  <si>
-    <t>正常添加-全部字段</t>
+    <t>{"name":"自品牌","firstLetter":"Z","logo":"https://test.com/logo.png"}</t>
   </si>
   <si>
     <t>{"name":"小红","firstLetter":"Q","sort":1,"factoryStatus":1,"showStatus":1,"logo":"https://test.com/logo.png","bigPic":"https://test.com/big.png","brandStory":"品牌故事"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"name":"自品牌","firstLetter":"Z","logo":"https://test.com/logo.png"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>code=200;message=操作成功</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>$.code=200;$.message=操作成功</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -140,28 +117,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -449,20 +415,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,54 +442,53 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    <row r="2" spans="1:7">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
         <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>